--- a/DatabaseSchema.xlsx
+++ b/DatabaseSchema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Setsu_GithubRepository\ReactNativeProject\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED46C3E-CB6F-4A27-90E2-752E0DD46487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4126C9D-EFB4-4B78-8B1A-4EC0059B6662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F1FCFFEC-14C9-4241-83CF-9FFF1A1881BF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
   <si>
     <t>db_code_blocks</t>
   </si>
@@ -110,9 +110,6 @@
     <t>itemDescription</t>
   </si>
   <si>
-    <t xml:space="preserve">skillName </t>
-  </si>
-  <si>
     <t>skillName</t>
   </si>
   <si>
@@ -171,6 +168,15 @@
   </si>
   <si>
     <t>enemySpd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skills </t>
+  </si>
+  <si>
+    <t>skillID</t>
+  </si>
+  <si>
+    <t>INTEGER REFERENCES skills(id)</t>
   </si>
 </sst>
 </file>
@@ -224,11 +230,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -573,26 +578,23 @@
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
     <col min="8" max="8" width="32.140625" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E2" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -603,7 +605,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -642,13 +644,13 @@
       </c>
       <c r="E5" s="1"/>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -669,7 +671,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -690,7 +692,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -711,7 +713,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -732,7 +734,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -753,7 +755,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -774,7 +776,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -782,12 +784,18 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="1"/>
+      <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
@@ -800,65 +808,83 @@
         <v>13</v>
       </c>
       <c r="E14" s="1"/>
+      <c r="G14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1"/>
+      <c r="G15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" t="s">
+      <c r="I16" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" t="s">
-        <v>27</v>
-      </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -866,7 +892,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -887,37 +913,37 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
         <v>30</v>
       </c>
-      <c r="C23" t="s">
-        <v>31</v>
-      </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1"/>
     </row>
@@ -926,7 +952,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
